--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2603-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2603-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A701826-BB57-461B-8B24-B257354E254F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F70DA9B9-4F72-4FB2-93FD-D128B6919617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C8E58A9B-1175-4F22-8C79-02976244EA9E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6F71AA89-C5E9-4486-B90F-E84BEF99D128}"/>
   </bookViews>
   <sheets>
     <sheet name="2603-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1514,29 +1514,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CE3E93-C154-4877-AD1C-15A90820442E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EE809-839A-427C-A911-5B84750D422D}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1570,7 +1569,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1606,7 +1605,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1658,7 +1657,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1726,7 +1725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1798,7 +1797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1942,7 +1941,7 @@
         <v>78.2</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -2014,7 +2013,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2086,7 +2085,7 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2230,7 +2229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2374,7 +2373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2662,7 +2661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2734,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2806,7 +2805,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2878,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2950,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -3022,7 +3021,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3094,7 +3093,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3166,7 +3165,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3238,7 +3237,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3310,7 +3309,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3382,7 +3381,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3454,7 +3453,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3598,7 +3597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3670,7 +3669,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3742,7 +3741,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>1996</v>
       </c>
@@ -3814,7 +3813,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1995</v>
       </c>
@@ -3886,7 +3885,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>1994</v>
       </c>
@@ -3958,7 +3957,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1993</v>
       </c>
@@ -4030,7 +4029,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>1992</v>
       </c>
@@ -4102,7 +4101,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41"/>
       <c r="B38" s="42"/>
       <c r="C38" s="18" t="s">
@@ -4130,7 +4129,7 @@
       <c r="W38" s="48"/>
       <c r="X38" s="44"/>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1991</v>
       </c>
@@ -4202,7 +4201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1990</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1989</v>
       </c>
@@ -4346,7 +4345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>1988</v>
       </c>
@@ -4418,7 +4417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1987</v>
       </c>
@@ -4490,7 +4489,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>1985</v>
       </c>
@@ -4562,7 +4561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1984</v>
       </c>
@@ -4634,7 +4633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
         <v>52</v>
       </c>
